--- a/Employee_Reports_wi48/Mark Roentgen Macatangay Delen Q0619.xlsx
+++ b/Employee_Reports_wi48/Mark Roentgen Macatangay Delen Q0619.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1145,11 +1145,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1194,11 +1194,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1316,9 +1316,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1330,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1416,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1453,11 +1465,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1502,11 +1514,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1933,7 +1945,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2028,7 +2040,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2057,7 +2069,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2098,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2115,7 +2127,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2144,7 +2156,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2173,7 +2185,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2202,7 +2214,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2243,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
